--- a/www/download/IND.surplus_value.empe_ls.r.pc.zdW13.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>131.43</t>
+          <t>1.31425563648117</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>125.48</t>
+          <t>1.25479851390372</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>135.74</t>
+          <t>1.35741046521898</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>133.32</t>
+          <t>1.33320469513524</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>122.99</t>
+          <t>1.22988157706943</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>132.91</t>
+          <t>1.32912182178093</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>139.65</t>
+          <t>1.39647956575537</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>129.05</t>
+          <t>1.29052322251919</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>114.96</t>
+          <t>1.14956090078817</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>0.883066343340924</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>0.800897423353554</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>83.56</t>
+          <t>0.835578578443454</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>79.12</t>
+          <t>0.791200692473612</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>96.47</t>
+          <t>0.964748149948828</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>105.12</t>
+          <t>1.05122569728457</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>0.815765208008174</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>0.900079378300322</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>124.19</t>
+          <t>1.24190179776997</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>122.67</t>
+          <t>1.22673794600456</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>119.84</t>
+          <t>1.19837533424678</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>129.39</t>
+          <t>1.29393818716353</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>126.19</t>
+          <t>1.26185214985986</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>123.94</t>
+          <t>1.2393604433362</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>0.591008944305468</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>0.948592890140581</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>92.63</t>
+          <t>0.926331071772838</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>0.913916945742336</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>103.16</t>
+          <t>1.03162376809177</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>106.57</t>
+          <t>1.06574092035797</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>1.22301003305378</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>0.0406046677140492</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.0169090584272724</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>0.0682219958710821</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>0.0772454436289973</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.0251363077155414</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.0343896566208736</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-0.090112698875097</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.5</t>
+          <t>-0.164974109726454</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-40.17</t>
+          <t>-0.401670527449917</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-34.41</t>
+          <t>-0.34410727941458</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-32.82</t>
+          <t>-0.328153256106741</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-0.31643358568357</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-0.25270835160328</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-0.180726946576867</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-22.97</t>
+          <t>-0.229711015328372</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>355.89</t>
+          <t>3.55894483336728</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>407.23</t>
+          <t>4.07233366386645</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>465.41</t>
+          <t>4.65410580753296</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>368.13</t>
+          <t>3.68125224502331</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>427.96</t>
+          <t>4.27958038860362</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>457.96</t>
+          <t>4.57964326817037</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>454.56</t>
+          <t>4.54561664129907</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>477.86</t>
+          <t>4.778606857481</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>400.6</t>
+          <t>4.00600968861281</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>512.33</t>
+          <t>5.12325029025554</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>539.01</t>
+          <t>5.39010070620185</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>564.86</t>
+          <t>5.64856678587077</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>534.52</t>
+          <t>5.34520949321187</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>515.94</t>
+          <t>5.1594405285221</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>460.89</t>
+          <t>4.60893756198279</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>658.33</t>
+          <t>6.583292245543</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>671.46</t>
+          <t>6.71458650734409</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>715.02</t>
+          <t>7.15016296676563</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>719.48</t>
+          <t>7.19479616301939</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>8.18998979019293</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>818.04</t>
+          <t>8.1803752642163</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>865.32</t>
+          <t>8.65319709873871</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>922.67</t>
+          <t>9.22666399292417</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>923.01</t>
+          <t>9.23008044809356</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>896.03</t>
+          <t>8.96034510556173</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>843.01</t>
+          <t>8.43013616804698</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>835.12</t>
+          <t>8.35117291887683</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>827.33</t>
+          <t>8.27331609440642</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>790.97</t>
+          <t>7.90972786068509</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>790.88</t>
+          <t>7.90876235060067</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>179.82</t>
+          <t>1.79817557462547</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>1.9798303672622</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>213.15</t>
+          <t>2.13148802996982</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>195.29</t>
+          <t>1.95287341151339</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>186.47</t>
+          <t>1.86470361220076</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>165.99</t>
+          <t>1.65985086611753</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>150.43</t>
+          <t>1.50426272508869</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>155.07</t>
+          <t>1.5506651705446</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>142.52</t>
+          <t>1.42515493410365</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>1.35899243152717</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>120.22</t>
+          <t>1.2022210781264</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>112.53</t>
+          <t>1.1253002804299</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>122.33</t>
+          <t>1.22329343293044</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>127.55</t>
+          <t>1.27551675901488</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>144.77</t>
+          <t>1.44769849673676</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-0.155319508636618</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-12.49</t>
+          <t>-0.124872313344725</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-0.0761371674533422</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.0182567376250379</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>0.0685853868287387</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>0.175315838613953</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>0.288897896645549</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>0.400998666314165</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>0.491508199695077</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>0.514205942883522</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>0.605560351192841</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>0.683717991765843</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>82.08</t>
+          <t>0.820783681833287</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>84.66</t>
+          <t>0.846632635919972</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>0.904210234001443</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>209.38</t>
+          <t>2.09378418895836</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>199.6</t>
+          <t>1.99598166086192</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>244.49</t>
+          <t>2.44485874467366</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>228.6</t>
+          <t>2.28600889654364</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>202.15</t>
+          <t>2.02149386643513</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>214.63</t>
+          <t>2.14633195913345</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>188.73</t>
+          <t>1.8872639560994</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>184.21</t>
+          <t>1.84214199255766</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>128.47</t>
+          <t>1.2847196678115</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>173.79</t>
+          <t>1.73790134496877</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>181.38</t>
+          <t>1.81377968031867</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>186.75</t>
+          <t>1.86747040559826</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>223.2</t>
+          <t>2.23200418259858</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>167.07</t>
+          <t>1.67070872589573</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>222.84</t>
+          <t>2.22836246111426</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>675.82</t>
+          <t>6.75820983129756</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>449.59</t>
+          <t>4.49592790536796</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>507.82</t>
+          <t>5.07822910245806</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>482.49</t>
+          <t>4.82489411389685</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>484.94</t>
+          <t>4.84938181454236</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>493.86</t>
+          <t>4.93858108148444</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>460.14</t>
+          <t>4.60137736188811</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>424.92</t>
+          <t>4.24915184091539</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>231.23</t>
+          <t>2.31234059738105</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>342.96</t>
+          <t>3.42961240311042</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>328.31</t>
+          <t>3.28305733566755</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>345.22</t>
+          <t>3.45217541678767</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>312.07</t>
+          <t>3.12070642623639</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>284.41</t>
+          <t>2.84412635284571</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>349.8</t>
+          <t>3.49800516649456</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>61.12</t>
+          <t>0.611205105295192</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>81.51</t>
+          <t>0.815081008193014</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>110.05</t>
+          <t>1.10046241749652</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>103.38</t>
+          <t>1.03380104706716</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>95.81</t>
+          <t>0.958074167815673</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>0.872532209182293</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>0.901277471350968</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>90.57</t>
+          <t>0.905698099497935</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>0.63230122335252</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>0.726017981930652</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>0.726816423703622</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>73.73</t>
+          <t>0.737286438393008</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>67.88</t>
+          <t>0.67882501697511</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>73.99</t>
+          <t>0.739898473426623</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>87.13</t>
+          <t>0.871342037038231</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>0.237468880832303</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.268826921581315</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.89</t>
+          <t>0.748872548676655</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>0.550344544059236</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>54.47</t>
+          <t>0.544676947566935</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>0.633660383181164</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>0.575657037512704</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>0.515238856000703</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>0.358801750017005</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>0.37275244903276</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>0.347042334789282</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>0.376631744634841</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>0.274238951370672</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>0.314890631680919</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>0.452862238752098</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>121.34</t>
+          <t>1.21343165137946</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>134.52</t>
+          <t>1.34524607621926</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>179.59</t>
+          <t>1.79589034266247</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>157.84</t>
+          <t>1.57842078417017</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>145.28</t>
+          <t>1.45276074291713</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>1.44299772232325</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>131.97</t>
+          <t>1.31968447783816</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>122.96</t>
+          <t>1.22958978507406</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>79.92</t>
+          <t>0.799159829531165</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>0.939436476080608</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>0.921818054317983</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>86.45</t>
+          <t>0.864473633679074</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>86.16</t>
+          <t>0.861587854667557</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>0.844439663810009</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>106.63</t>
+          <t>1.06629431695406</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>608.4</t>
+          <t>6.08402331360892</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>543.48</t>
+          <t>5.43479379624527</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>518.78</t>
+          <t>5.1877527317346</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>476.32</t>
+          <t>4.76318124452521</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>526.54</t>
+          <t>5.26538189416844</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>444.12</t>
+          <t>4.44121839897547</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>426.96</t>
+          <t>4.26957877188468</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>313.07</t>
+          <t>3.13068485341804</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>160.25</t>
+          <t>1.60249789143989</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>2.35995937921155</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>255.61</t>
+          <t>2.55609249652922</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>247.96</t>
+          <t>2.47962899932976</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>193.26</t>
+          <t>1.93257758043651</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>146.16</t>
+          <t>1.46157758435638</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>161.49</t>
+          <t>1.61489704883957</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>67.88</t>
+          <t>0.678808517587111</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>61.74</t>
+          <t>0.617445987798986</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>93.44</t>
+          <t>0.934401357655074</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>0.874005939145347</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>0.894986751078207</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>111.85</t>
+          <t>1.118500024181</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>105.41</t>
+          <t>1.05411491972216</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>1.04100729506436</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>0.706477103385444</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>0.768034046208517</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>0.732289992871588</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>67.75</t>
+          <t>0.677464862648471</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>0.652606092834473</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>0.560402925820069</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>0.654505799821726</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>0.806028601284992</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>85.22</t>
+          <t>0.852184091283142</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>112.27</t>
+          <t>1.12265275010738</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>0.904086035602903</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>77.83</t>
+          <t>0.778325120942859</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>0.760384535693721</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>66.39</t>
+          <t>0.663941130580943</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>0.561389744697619</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>0.18832808664603</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>0.38533962877508</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>0.371606847450248</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>0.387169216491804</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>0.443799532857221</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>0.420951387886252</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>0.536533646031875</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>119.86</t>
+          <t>1.19860535663921</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>119.04</t>
+          <t>1.19040708764365</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>142.14</t>
+          <t>1.42144306055038</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>127.71</t>
+          <t>1.27713236528212</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>114.17</t>
+          <t>1.14166241663624</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>104.95</t>
+          <t>1.04952172346852</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>93.18</t>
+          <t>0.931834960889978</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>86.04</t>
+          <t>0.860362018677138</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>0.739063494699558</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>63.59</t>
+          <t>0.635894011036956</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>0.635767207225727</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>0.627974321711419</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>0.666949404828705</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>81.28</t>
+          <t>0.812785421139903</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>0.948080234162674</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>219.23</t>
+          <t>2.19234841158376</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>213.21</t>
+          <t>2.13211896592349</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>236.22</t>
+          <t>2.36220542605414</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>249.69</t>
+          <t>2.49690223420798</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>238.94</t>
+          <t>2.38941967141978</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>232.69</t>
+          <t>2.32687569784742</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>252.52</t>
+          <t>2.52515252343443</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>208.71</t>
+          <t>2.08712566498733</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>168.35</t>
+          <t>1.68345270880811</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>204.03</t>
+          <t>2.04032207380639</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>210.69</t>
+          <t>2.10685051118074</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>197.54</t>
+          <t>1.97536150274378</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>186.91</t>
+          <t>1.86908877285771</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>177.43</t>
+          <t>1.77430203764379</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>175.4</t>
+          <t>1.75398153787404</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>358.31</t>
+          <t>3.58313207681237</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>375.38</t>
+          <t>3.75381509088594</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>404.16</t>
+          <t>4.04161320636151</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>419.46</t>
+          <t>4.19464746422769</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>440.93</t>
+          <t>4.40930208679537</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>419.94</t>
+          <t>4.19943110870205</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>433.95</t>
+          <t>4.33953576653969</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>396.57</t>
+          <t>3.96568837188784</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>197.87</t>
+          <t>1.97873713891341</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>452.45</t>
+          <t>4.52450445346788</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>463.44</t>
+          <t>4.63437754271154</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>496.47</t>
+          <t>4.96470204138209</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>470.19</t>
+          <t>4.70190677631748</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>499.57</t>
+          <t>4.99566946989334</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>548.98</t>
+          <t>5.48975713592048</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>154.84</t>
+          <t>1.54843876098405</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>150.12</t>
+          <t>1.50118652845698</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>195.09</t>
+          <t>1.95092922231127</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>190.06</t>
+          <t>1.90062962684799</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>186.03</t>
+          <t>1.860282241787</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>181.1</t>
+          <t>1.81099501736071</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>190.41</t>
+          <t>1.9040666650139</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>196.55</t>
+          <t>1.96550216312868</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>169.99</t>
+          <t>1.69991691994959</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>191.91</t>
+          <t>1.9191471745124</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>178.59</t>
+          <t>1.78586516244644</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>162.67</t>
+          <t>1.62668734218435</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>152.73</t>
+          <t>1.52733054690358</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>157.11</t>
+          <t>1.57114353458437</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>145.63</t>
+          <t>1.45630708551754</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>151.51</t>
+          <t>1.5151456152938</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>177.27</t>
+          <t>1.77265240704484</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1.6900469119863</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>183.77</t>
+          <t>1.83768029039055</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>196.52</t>
+          <t>1.96523714742699</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>2.11279077194225</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>210.07</t>
+          <t>2.10068177329121</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>2.15497172114966</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>201.96</t>
+          <t>2.01956021003354</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>186.32</t>
+          <t>1.86324952362587</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>172.65</t>
+          <t>1.72648347758745</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>164.96</t>
+          <t>1.64959749993619</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>166.62</t>
+          <t>1.66619906558147</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>176.3</t>
+          <t>1.76298981418173</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>165.53</t>
+          <t>1.65526560733732</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>1.13198066926737</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>1.14307195118878</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>153.25</t>
+          <t>1.53248074339736</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>169.06</t>
+          <t>1.69062470318687</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>173.92</t>
+          <t>1.73915449340913</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>1.72662050214731</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>148.02</t>
+          <t>1.48022163832703</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>135.83</t>
+          <t>1.35831876580005</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>160.59</t>
+          <t>1.60588067529226</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>177.77</t>
+          <t>1.77773061118419</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>1.40297925291121</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>1.68503504574269</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>126.57</t>
+          <t>1.26568647399142</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>104.91</t>
+          <t>1.04908957809148</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>85.02</t>
+          <t>0.85024229148628</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>98.16</t>
+          <t>0.981584973199817</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>110.84</t>
+          <t>1.10843491811799</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>135.83</t>
+          <t>1.35831728448125</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>140.89</t>
+          <t>1.4088686626705</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>140.77</t>
+          <t>1.40774794919092</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>143.26</t>
+          <t>1.4325977530046</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>131.14</t>
+          <t>1.31137440094764</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>125.84</t>
+          <t>1.25840959022602</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>0.802404438399684</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>92.79</t>
+          <t>0.927894357412414</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>0.929552782523593</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>0.912681470988137</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>97.75</t>
+          <t>0.977481614057802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>89.01</t>
+          <t>0.890149743109295</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>1.08503945645491</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>0.726847024726679</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>98.17</t>
+          <t>0.981653168534721</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>119.94</t>
+          <t>1.19944987828472</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>126.19</t>
+          <t>1.26189900762251</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>113.06</t>
+          <t>1.13062518981786</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>0.995848549112806</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>104.67</t>
+          <t>1.04666510114032</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>119.44</t>
+          <t>1.19438083459644</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>111.03</t>
+          <t>1.110292923789</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>103.08</t>
+          <t>1.0307827167203</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>1.04838658801453</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>116.67</t>
+          <t>1.16673799153937</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>139.27</t>
+          <t>1.3926883753017</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>1.47043743851314</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>140.92</t>
+          <t>1.40921482219226</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>150.6</t>
+          <t>1.50601824917789</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>162.58</t>
+          <t>1.6257578408068</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>192.67</t>
+          <t>1.92673908101042</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>225.34</t>
+          <t>2.25335138950871</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>2.27792295114897</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>219.48</t>
+          <t>2.19475281214182</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>241.34</t>
+          <t>2.41344021121</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>236.5</t>
+          <t>2.36497292366573</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>214.38</t>
+          <t>2.14378324044262</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>215.71</t>
+          <t>2.15707915854334</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>205.89</t>
+          <t>2.05893295351663</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>196.89</t>
+          <t>1.96892138885461</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>202.86</t>
+          <t>2.02863314593409</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>228.46</t>
+          <t>2.28462823212255</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>251.41</t>
+          <t>2.5141191803834</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>453.27</t>
+          <t>4.53265282243995</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>409.05</t>
+          <t>4.09053351773152</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>408.31</t>
+          <t>4.08308806834813</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>350.14</t>
+          <t>3.50140311154743</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>343.86</t>
+          <t>3.43859169174989</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>338.54</t>
+          <t>3.3854495070012</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>328.7</t>
+          <t>3.28700492714821</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>322.84</t>
+          <t>3.22843801127306</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>210.14</t>
+          <t>2.10141111214789</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>335.94</t>
+          <t>3.35943149855283</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>328.98</t>
+          <t>3.28978371019045</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>313.2</t>
+          <t>3.13195758889831</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>257.55</t>
+          <t>2.5755476008327</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>211.6</t>
+          <t>2.11600501393159</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>219.14</t>
+          <t>2.19137955641329</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>0.50089830956949</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>76.18</t>
+          <t>0.761776025859905</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>115.42</t>
+          <t>1.15422583945507</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>132.03</t>
+          <t>1.320298764472</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>137.78</t>
+          <t>1.37782466161055</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>144.98</t>
+          <t>1.44975337136139</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>168.63</t>
+          <t>1.6862521388975</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>1.4769556802295</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>0.78015122321729</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>128.52</t>
+          <t>1.28517628699668</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>118.43</t>
+          <t>1.18429526723172</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>123.68</t>
+          <t>1.23683464545824</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>158.71</t>
+          <t>1.58710883910359</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>123.76</t>
+          <t>1.23764566927243</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>176.11</t>
+          <t>1.7611339384127</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>442.64</t>
+          <t>4.42638462364364</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>403.51</t>
+          <t>4.03511610553814</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>3.82996014818765</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>388.57</t>
+          <t>3.88570795056383</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>417.88</t>
+          <t>4.17884495177585</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>494.24</t>
+          <t>4.94242338277318</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>502.36</t>
+          <t>5.02361580379325</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>525.82</t>
+          <t>5.2582028498374</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>353.54</t>
+          <t>3.53538611602246</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>510.27</t>
+          <t>5.10274724196688</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>438.51</t>
+          <t>4.38510273998609</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>386.2</t>
+          <t>3.86197301730623</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>334.22</t>
+          <t>3.34217352706568</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>282.15</t>
+          <t>2.82145927100508</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>372.26</t>
+          <t>3.72257760246052</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>889.82</t>
+          <t>8.89823859916315</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>984.62</t>
+          <t>9.84617987661389</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1066.88</t>
+          <t>10.6688001242543</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>10.0640291340098</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>949.09</t>
+          <t>9.4908952799602</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>922.95</t>
+          <t>9.22950510973491</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>843.68</t>
+          <t>8.43680564371612</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>860.21</t>
+          <t>8.60209550304054</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>886.74</t>
+          <t>8.86736906278561</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>925.84</t>
+          <t>9.25844847729495</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>920.29</t>
+          <t>9.20290432079819</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1013.35</t>
+          <t>10.1335282459962</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1065.97</t>
+          <t>10.6596671631506</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1140.65</t>
+          <t>11.4064705739856</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1151.43</t>
+          <t>11.5143283311061</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>225.28</t>
+          <t>2.25279443018933</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>208.73</t>
+          <t>2.08734496248782</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>278.72</t>
+          <t>2.78717914674489</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>2.46496794517761</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>213.2</t>
+          <t>2.13203261175639</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>196.56</t>
+          <t>1.96558118778546</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>124.42</t>
+          <t>1.24422402646664</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>148.51</t>
+          <t>1.4850691667259</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>85.62</t>
+          <t>0.856222715091346</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>192.17</t>
+          <t>1.92171427489607</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>197.17</t>
+          <t>1.97173673477275</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>206.52</t>
+          <t>2.06517482145793</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>192.39</t>
+          <t>1.9238974574373</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>149.47</t>
+          <t>1.49468309779079</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>191.12</t>
+          <t>1.91119534579966</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.0255039446512572</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>0.0406544200004442</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>0.578378761957674</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>0.304674410428773</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>0.260506304032032</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>0.316849026218328</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>0.184091273363136</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>0.0848229259076181</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-0.0685654327924645</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>0.145364701749395</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>0.18764933210623</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>0.180347546695066</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0.170037159754293</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>0.0647927549681964</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0.104405020451433</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>173.34</t>
+          <t>1.73344256596905</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>163.46</t>
+          <t>1.63458443730666</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>165.89</t>
+          <t>1.65889995247194</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>155.17</t>
+          <t>1.55168444951207</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>173.89</t>
+          <t>1.73890145972014</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>198.91</t>
+          <t>1.98913385677603</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>289.58</t>
+          <t>2.89582799670711</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>308.01</t>
+          <t>3.08005022415101</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>198.02</t>
+          <t>1.98022148443042</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>370.43</t>
+          <t>3.70431387926385</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>353.03</t>
+          <t>3.53025563306027</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>369.24</t>
+          <t>3.69239716513386</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>389.99</t>
+          <t>3.89994675502803</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>321.43</t>
+          <t>3.2143237340198</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>362.27</t>
+          <t>3.62272525193164</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>178.07</t>
+          <t>1.78066382670264</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>1.74185943174322</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>215.53</t>
+          <t>2.15531887499254</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>184.51</t>
+          <t>1.84505191159932</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>193.27</t>
+          <t>1.93269073616965</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>188.63</t>
+          <t>1.886338598006</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1.77995102820869</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>184.68</t>
+          <t>1.84677993407263</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>139.74</t>
+          <t>1.3974184152997</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>192.25</t>
+          <t>1.92254878647233</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>199.35</t>
+          <t>1.99350044348129</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>226.15</t>
+          <t>2.26154202467814</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>222.88</t>
+          <t>2.22882770652915</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>206.12</t>
+          <t>2.06115224284902</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>254.61</t>
+          <t>2.54607928562586</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>206.65</t>
+          <t>2.06648514616398</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>212.9</t>
+          <t>2.1289716279415</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>249.17</t>
+          <t>2.49171767111458</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>170.68</t>
+          <t>1.70675823240049</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>184.1</t>
+          <t>1.84102950222647</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>1.38299779520619</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>122.68</t>
+          <t>1.22681210841798</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>204.85</t>
+          <t>2.04849515576797</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>161.76</t>
+          <t>1.61761342785971</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>270.29</t>
+          <t>2.70285378119809</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>218.45</t>
+          <t>2.18446289376448</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>242.29</t>
+          <t>2.4228937054666</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>222.77</t>
+          <t>2.22772009548478</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>198.06</t>
+          <t>1.98058322615893</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>243.35</t>
+          <t>2.43354125126611</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303.49</t>
+          <t>3.03494921409769</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>281.54</t>
+          <t>2.81539155436017</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>325.7</t>
+          <t>3.25698318708048</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>350.57</t>
+          <t>3.50572278131389</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>349.5</t>
+          <t>3.49503700009046</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>309.4</t>
+          <t>3.09398641690903</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>3.399985294325</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>315.17</t>
+          <t>3.1516609617119</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>288.29</t>
+          <t>2.88293057652891</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>287.6</t>
+          <t>2.87601624677211</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>272.05</t>
+          <t>2.72048025289798</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>277.26</t>
+          <t>2.77260977456231</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>244.87</t>
+          <t>2.44870394989469</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>202.26</t>
+          <t>2.02264677206853</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>207.01</t>
+          <t>2.07006435812865</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>717.75</t>
+          <t>7.17753746337454</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>684.43</t>
+          <t>6.84434227580809</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>711.37</t>
+          <t>7.11374033968104</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>699.46</t>
+          <t>6.99457627458498</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>757.91</t>
+          <t>7.57909654764331</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>774.06</t>
+          <t>7.74061052866011</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>746.07</t>
+          <t>7.46070573545025</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>725.92</t>
+          <t>7.25920034192533</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>339.94</t>
+          <t>3.39941113600299</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>495.87</t>
+          <t>4.9586845062865</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>528.77</t>
+          <t>5.28768308879413</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>492.58</t>
+          <t>4.92578807035931</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>388.62</t>
+          <t>3.88616184023553</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>311.68</t>
+          <t>3.11681714677729</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>232.03</t>
+          <t>2.32031873070805</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>164.95</t>
+          <t>1.64951361331779</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>172.91</t>
+          <t>1.72914601578082</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>212.49</t>
+          <t>2.12489029417878</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>1.95500155750618</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>208.93</t>
+          <t>2.08928857441758</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>203.49</t>
+          <t>2.03490072330501</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>186.48</t>
+          <t>1.86479295362879</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>182.22</t>
+          <t>1.82218389335035</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>158.47</t>
+          <t>1.58471286563271</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>177.16</t>
+          <t>1.77156063970986</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>189.65</t>
+          <t>1.89648173715877</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>190.64</t>
+          <t>1.90640841604813</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>177.86</t>
+          <t>1.77855776124857</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>103.88</t>
+          <t>1.03880709958542</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>114.59</t>
+          <t>1.14587906098868</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>69.27</t>
+          <t>0.692680566612859</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>67.59</t>
+          <t>0.675899112329598</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>96.37</t>
+          <t>0.963729776865059</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>82.18</t>
+          <t>0.821791689136704</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>83.79</t>
+          <t>0.837948724849991</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>0.682489755190317</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>65.98</t>
+          <t>0.65976120085269</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>0.609371073381924</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>0.356578457783058</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>0.415758089095112</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>0.367971556656463</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>0.362782764109314</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>0.271681569628307</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>0.369660649708273</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0.580017116374236</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>285.88</t>
+          <t>2.85878918423052</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>253.76</t>
+          <t>2.53764815413566</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>244.18</t>
+          <t>2.44178451943423</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>239.15</t>
+          <t>2.39149178614165</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>235.49</t>
+          <t>2.35486318284902</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>288.62</t>
+          <t>2.88616456009314</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>329.36</t>
+          <t>3.2936205059262</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>379.68</t>
+          <t>3.79678819108811</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>368.15</t>
+          <t>3.68146455728611</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>335.75</t>
+          <t>3.35750155755253</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>370.23</t>
+          <t>3.70230606053488</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>402.52</t>
+          <t>4.02521989035449</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>403.35</t>
+          <t>4.03349273397235</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>190.17</t>
+          <t>1.90168675006504</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>230.44</t>
+          <t>2.30440424085554</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>147.89</t>
+          <t>1.47890231313374</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>130.18</t>
+          <t>1.30177833604042</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>166.46</t>
+          <t>1.66464261742678</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>178.93</t>
+          <t>1.78927212047665</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>188.07</t>
+          <t>1.88068334887084</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>177.53</t>
+          <t>1.77528640364911</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>166.89</t>
+          <t>1.66889572715515</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>173.88</t>
+          <t>1.73884992082637</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>173.19</t>
+          <t>1.73193372538832</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>176.01</t>
+          <t>1.760110509789</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>175.92</t>
+          <t>1.75923109758322</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>184.81</t>
+          <t>1.84810655750212</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>215.28</t>
+          <t>2.15275537667253</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>211.73</t>
+          <t>2.1173437624403</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>261.32</t>
+          <t>2.61316891222759</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>221.45</t>
+          <t>2.21448815024027</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>229.8</t>
+          <t>2.29802628155439</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>214.22</t>
+          <t>2.14216151910239</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>220.43</t>
+          <t>2.20426708232231</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>218.04</t>
+          <t>2.18041124652676</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>191.02</t>
+          <t>1.9101768556077</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>181.16</t>
+          <t>1.81155475343078</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>176.51</t>
+          <t>1.76512550285957</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>166.65</t>
+          <t>1.66649410277918</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>167.72</t>
+          <t>1.67718000398943</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>172.53</t>
+          <t>1.72526578564779</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>179.39</t>
+          <t>1.79389992934752</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>196.7</t>
+          <t>1.96699038861812</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>224.06</t>
+          <t>2.24063212500669</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>229.65</t>
+          <t>2.29650871209463</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>115.58</t>
+          <t>1.15576654678628</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>127.85</t>
+          <t>1.2784595018725</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>132.94</t>
+          <t>1.32944786041268</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>139.61</t>
+          <t>1.39611467935391</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>143.09</t>
+          <t>1.43085564245665</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>134.69</t>
+          <t>1.34689465660397</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>140.35</t>
+          <t>1.40346228569705</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>147.46</t>
+          <t>1.47462063062402</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>125.89</t>
+          <t>1.25886136336434</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>166.19</t>
+          <t>1.66186700853734</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>159.34</t>
+          <t>1.59340604570912</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>154.99</t>
+          <t>1.54986512599455</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>160.35</t>
+          <t>1.60352527139558</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>151.61</t>
+          <t>1.51614614455436</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>177.45</t>
+          <t>1.77449574672923</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>0.738702311202255</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>82.07</t>
+          <t>0.820723623011532</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>89.17</t>
+          <t>0.891670336307912</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>0.958420144198767</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>105.23</t>
+          <t>1.05231516049425</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>112.21</t>
+          <t>1.12207680686348</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>119.53</t>
+          <t>1.19529940771004</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>127.82</t>
+          <t>1.27821420633873</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>120.71</t>
+          <t>1.20714370684468</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>131.6</t>
+          <t>1.31604171336777</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>132.44</t>
+          <t>1.32444910000037</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>133.88</t>
+          <t>1.33884554377347</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>141.37</t>
+          <t>1.41372548973206</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>140.41</t>
+          <t>1.4040986768142</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>149.12</t>
+          <t>1.49117276525636</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
